--- a/artfynd/A 54527-2023 artfynd.xlsx
+++ b/artfynd/A 54527-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54527-2023 artfynd.xlsx
+++ b/artfynd/A 54527-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102532162</v>
+        <v>102532416</v>
       </c>
       <c r="B2" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695468.2410985277</v>
+        <v>695441</v>
       </c>
       <c r="R2" t="n">
-        <v>6322996.331503508</v>
+        <v>6322947</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,21 +752,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,11 +765,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,47 +781,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102532169</v>
+        <v>102532348</v>
       </c>
       <c r="B3" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>201164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695459.4732727301</v>
+        <v>695389</v>
       </c>
       <c r="R3" t="n">
-        <v>6322962.10613915</v>
+        <v>6322978</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -883,21 +868,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkfuktäng nära körväg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,37 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102532124</v>
+        <v>102532158</v>
       </c>
       <c r="B4" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695389.3053758031</v>
+        <v>695421</v>
       </c>
       <c r="R4" t="n">
-        <v>6322978.429373053</v>
+        <v>6322972</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,21 +970,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1026,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Fuktglänta i kratttallskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1044,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102532164</v>
+        <v>102532127</v>
       </c>
       <c r="B5" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,26 +1015,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1093,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695467.2214950362</v>
+        <v>695398</v>
       </c>
       <c r="R5" t="n">
-        <v>6322983.195015284</v>
+        <v>6323000</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1126,21 +1081,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkfuktäng.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102532138</v>
+        <v>102532128</v>
       </c>
       <c r="B6" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,34 +1126,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695423.4807628623</v>
+        <v>695420</v>
       </c>
       <c r="R6" t="n">
-        <v>6323041.665196436</v>
+        <v>6322998</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1243,21 +1192,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1269,7 +1208,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkgrus på åsrygg.</t>
+          <t>Kalkfuktäng.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1287,15 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102532144</v>
+        <v>102532131</v>
       </c>
       <c r="B7" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695498.316231336</v>
+        <v>695420</v>
       </c>
       <c r="R7" t="n">
-        <v>6323065.373136531</v>
+        <v>6323021</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,21 +1303,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1319,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkfuktäng.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1413,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102532127</v>
+        <v>102532134</v>
       </c>
       <c r="B8" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1367,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1462,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695398.1443581635</v>
+        <v>695443</v>
       </c>
       <c r="R8" t="n">
-        <v>6322999.569437722</v>
+        <v>6323040</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,21 +1414,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1521,7 +1430,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Fuktsvacka mellan kalkgrusåsar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102532174</v>
+        <v>102532137</v>
       </c>
       <c r="B9" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,20 +1476,29 @@
           <t>(L.) Scop.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695416.1889328491</v>
+        <v>695426</v>
       </c>
       <c r="R9" t="n">
-        <v>6322906.619633982</v>
+        <v>6323040</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,21 +1525,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1638,7 +1541,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grustagskant.</t>
+          <t>Kalkgrus på åsrygg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1656,15 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102532148</v>
+        <v>102532144</v>
       </c>
       <c r="B10" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1589,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1705,13 +1603,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>695492.780973153</v>
+        <v>695498</v>
       </c>
       <c r="R10" t="n">
-        <v>6323055.295833839</v>
+        <v>6323065</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1738,19 +1636,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,15 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102532161</v>
+        <v>102532147</v>
       </c>
       <c r="B11" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,37 +1681,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695468.2410985277</v>
+        <v>695495</v>
       </c>
       <c r="R11" t="n">
-        <v>6322996.331503508</v>
+        <v>6323076</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,19 +1747,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,15 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102532166</v>
+        <v>102532148</v>
       </c>
       <c r="B12" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,26 +1792,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1948,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695465.4256291357</v>
+        <v>695493</v>
       </c>
       <c r="R12" t="n">
-        <v>6322974.930032834</v>
+        <v>6323055</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1981,19 +1858,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,15 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102532133</v>
+        <v>102532165</v>
       </c>
       <c r="B13" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,34 +1903,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695418.9267925752</v>
+        <v>695467</v>
       </c>
       <c r="R13" t="n">
-        <v>6323022.363394742</v>
+        <v>6322973</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2098,21 +1969,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +1985,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Fuktsvacka mellan kalkgrusåsar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2145,12 +2006,7 @@
         <v>102532167</v>
       </c>
       <c r="B14" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695459.4732727301</v>
+        <v>695459</v>
       </c>
       <c r="R14" t="n">
-        <v>6322962.10613915</v>
+        <v>6322962</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2224,19 +2080,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,15 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102532170</v>
+        <v>102532174</v>
       </c>
       <c r="B15" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,21 +2125,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2308,13 +2149,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695439.8581861702</v>
+        <v>695416</v>
       </c>
       <c r="R15" t="n">
-        <v>6322937.730654185</v>
+        <v>6322907</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2341,19 +2182,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,12 +2219,7 @@
         <v>102532185</v>
       </c>
       <c r="B16" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695382.5317935941</v>
+        <v>695383</v>
       </c>
       <c r="R16" t="n">
-        <v>6322890.307731735</v>
+        <v>6322890</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2458,19 +2284,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2502,15 +2318,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102532152</v>
+        <v>102532189</v>
       </c>
       <c r="B17" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,21 +2329,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2542,13 +2353,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695485.9180982814</v>
+        <v>695382</v>
       </c>
       <c r="R17" t="n">
-        <v>6323038.611763746</v>
+        <v>6322887</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2575,19 +2386,14 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridd mot S.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2407,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kraftledningsgata, igenväxande alvarmark på kalkgrus i grustag.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2619,15 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102532155</v>
+        <v>102532195</v>
       </c>
       <c r="B18" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,26 +2436,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2668,13 +2469,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695477.0539753082</v>
+        <v>695355</v>
       </c>
       <c r="R18" t="n">
-        <v>6323018.015809689</v>
+        <v>6322903</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2701,33 +2502,24 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Körvägkant, alvarartad.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2748,12 +2540,7 @@
         <v>102532142</v>
       </c>
       <c r="B19" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2785,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695500.2146784938</v>
+        <v>695500</v>
       </c>
       <c r="R19" t="n">
-        <v>6323071.461449822</v>
+        <v>6323071</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2818,19 +2605,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,15 +2639,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102532145</v>
+        <v>102532155</v>
       </c>
       <c r="B20" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,21 +2650,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2911,13 +2683,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695498.316231336</v>
+        <v>695477</v>
       </c>
       <c r="R20" t="n">
-        <v>6323065.373136531</v>
+        <v>6323018</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,19 +2716,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,15 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102532348</v>
+        <v>102532162</v>
       </c>
       <c r="B21" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3004,41 +2761,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201164</v>
+        <v>220164</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3047,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695389.3053758031</v>
+        <v>695468</v>
       </c>
       <c r="R21" t="n">
-        <v>6322978.429373053</v>
+        <v>6322996</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -3080,21 +2827,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3106,7 +2843,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkfuktäng nära körväg.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3124,15 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102532130</v>
+        <v>102532163</v>
       </c>
       <c r="B22" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,37 +2872,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695431.8518609924</v>
+        <v>695462</v>
       </c>
       <c r="R22" t="n">
-        <v>6323014.792832303</v>
+        <v>6322994</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3197,21 +2938,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +2954,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3241,15 +2972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102532137</v>
+        <v>102532164</v>
       </c>
       <c r="B23" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,26 +2983,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3290,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695425.7642958617</v>
+        <v>695467</v>
       </c>
       <c r="R23" t="n">
-        <v>6323039.59153133</v>
+        <v>6322983</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3323,21 +3049,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3349,7 +3065,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkgrus på åsrygg.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3367,15 +3083,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102532135</v>
+        <v>102532166</v>
       </c>
       <c r="B24" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,34 +3094,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695436.9059075983</v>
+        <v>695465</v>
       </c>
       <c r="R24" t="n">
-        <v>6323046.6611532</v>
+        <v>6322975</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3440,21 +3160,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3466,7 +3176,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkgrus på åsrygg.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3484,15 +3194,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102532186</v>
+        <v>102532169</v>
       </c>
       <c r="B25" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3500,26 +3205,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3527,21 +3232,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695382.5317935941</v>
+        <v>695459</v>
       </c>
       <c r="R25" t="n">
-        <v>6322890.307731735</v>
+        <v>6322962</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3571,26 +3271,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3602,7 +3287,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, igenväxande alvarmark på kalkgrus i grustag.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3620,62 +3305,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102532147</v>
+        <v>102532192</v>
       </c>
       <c r="B26" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695494.5571386558</v>
+        <v>695355</v>
       </c>
       <c r="R26" t="n">
-        <v>6323075.557219479</v>
+        <v>6322903</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3702,21 +3373,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3728,7 +3389,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kraftledningsgata, igenväxande alvarmark på kalkgrus.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3746,15 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102532131</v>
+        <v>102532124</v>
       </c>
       <c r="B27" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3762,46 +3418,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695420.0685625483</v>
+        <v>695389</v>
       </c>
       <c r="R27" t="n">
-        <v>6323021.326555851</v>
+        <v>6322978</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3828,19 +3475,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3872,15 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102532134</v>
+        <v>102532130</v>
       </c>
       <c r="B28" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3888,43 +3520,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695442.6917557111</v>
+        <v>695432</v>
       </c>
       <c r="R28" t="n">
-        <v>6323039.844619098</v>
+        <v>6323015</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3954,21 +3577,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3980,7 +3593,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktsvacka mellan kalkgrusåsar.</t>
+          <t>Kalkfuktäng.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3998,15 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102532128</v>
+        <v>102532132</v>
       </c>
       <c r="B29" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4014,43 +3622,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695420.0559851663</v>
+        <v>695420</v>
       </c>
       <c r="R29" t="n">
-        <v>6322998.421422986</v>
+        <v>6323021</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -4080,19 +3679,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,15 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102532143</v>
+        <v>102532133</v>
       </c>
       <c r="B30" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4164,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695500.2146784938</v>
+        <v>695419</v>
       </c>
       <c r="R30" t="n">
-        <v>6323071.461449822</v>
+        <v>6323022</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4197,21 +3781,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4223,7 +3797,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Fuktsvacka mellan kalkgrusåsar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4241,15 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102532165</v>
+        <v>102532135</v>
       </c>
       <c r="B31" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4257,43 +3826,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695466.5930933622</v>
+        <v>695437</v>
       </c>
       <c r="R31" t="n">
-        <v>6322973.349052631</v>
+        <v>6323047</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4323,21 +3883,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4349,7 +3899,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkgrus på åsrygg.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4367,15 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102532132</v>
+        <v>102532138</v>
       </c>
       <c r="B32" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4407,10 +3952,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695420.0685625483</v>
+        <v>695423</v>
       </c>
       <c r="R32" t="n">
-        <v>6323021.326555851</v>
+        <v>6323042</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4440,21 +3985,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4001,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Kalkgrus på åsrygg.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4484,15 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102532163</v>
+        <v>102532143</v>
       </c>
       <c r="B33" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4500,43 +4030,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695462.3462999074</v>
+        <v>695500</v>
       </c>
       <c r="R33" t="n">
-        <v>6322993.872024042</v>
+        <v>6323071</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4566,19 +4087,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4610,15 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102532153</v>
+        <v>102532145</v>
       </c>
       <c r="B34" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4645,7 +4151,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4659,10 +4165,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695479.8888932447</v>
+        <v>695498</v>
       </c>
       <c r="R34" t="n">
-        <v>6323027.420427391</v>
+        <v>6323065</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4692,24 +4198,9 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spridd 10 m V</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4741,37 +4232,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102532158</v>
+        <v>102532152</v>
       </c>
       <c r="B35" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219811</v>
+        <v>221849</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4781,13 +4267,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695420.7682714295</v>
+        <v>695486</v>
       </c>
       <c r="R35" t="n">
-        <v>6322971.732895401</v>
+        <v>6323039</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4814,21 +4300,11 @@
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-28</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4840,7 +4316,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Fuktglänta i kratttallskog.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4858,15 +4334,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104463445</v>
+        <v>102532153</v>
       </c>
       <c r="B36" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4891,28 +4362,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vamlingbo Västlands, Gotland, Gtl</t>
+          <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695443.8350493395</v>
+        <v>695480</v>
       </c>
       <c r="R36" t="n">
-        <v>6322946.098565365</v>
+        <v>6323027</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4936,22 +4408,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd 10 m V</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4960,22 +4427,569 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>102532161</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>695468</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6322996</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vamlingbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>102532170</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695440</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6322938</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vamlingbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Grustagskant.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>102532188</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>695382</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6322887</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vamlingbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, igenväxande alvarmark på kalkgrus i grustag.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104463445</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vamlingbo Västlands, Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>695444</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6322946</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vamlingbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Anders Carlberg</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Anders Carlberg, Håkan Persson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>102532186</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vamlingbo, Sigrajvs 1:43 (2) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>695383</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6322890</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vamlingbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minsta antal..</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, igenväxande alvarmark på kalkgrus i grustag.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54527-2023 artfynd.xlsx
+++ b/artfynd/A 54527-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532416</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532131</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532134</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532144</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532147</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532148</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532165</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2111,6 +2176,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532167</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2213,6 +2283,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532174</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532185</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532189</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2534,6 +2619,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532195</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2636,6 +2726,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532142</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2747,6 +2842,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532155</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2858,6 +2958,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532162</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2969,6 +3074,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532163</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3080,6 +3190,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532164</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3191,6 +3306,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532166</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3302,6 +3422,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532169</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3404,6 +3529,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532192</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3506,6 +3636,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532124</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3608,6 +3743,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532130</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3710,6 +3850,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532132</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3812,6 +3957,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532133</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3914,6 +4064,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532135</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4016,6 +4171,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532138</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4118,6 +4278,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532143</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4229,6 +4394,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532145</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4331,6 +4501,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532152</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4447,6 +4622,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532153</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4549,6 +4729,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532161</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4651,6 +4836,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532170</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4753,6 +4943,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532188</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4869,6 +5064,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104463445</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4990,8 +5190,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532186</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>